--- a/output/pdf_financials_xlsx/TAJ.xlsx
+++ b/output/pdf_financials_xlsx/TAJ.xlsx
@@ -1234,37 +1234,37 @@
         <v>0.24115</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.199466</v>
+        <v>-0.199466</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>1.923305</v>
+        <v>-1.923305</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.307874</v>
+        <v>-0.307874</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.418264</v>
+        <v>-0.418264</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.813829</v>
+        <v>-0.813829</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.658291</v>
+        <v>-0.658291</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>1.601392</v>
+        <v>-1.601392</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>3.253992</v>
+        <v>-3.253992</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>0.404814</v>
+        <v>-0.404814</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0.456605</v>
+        <v>-0.456605</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>4.897817</v>
+        <v>-4.897817</v>
       </c>
     </row>
     <row r="17">
@@ -1277,16 +1277,16 @@
         <v>-0.025</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.195816</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0.03</v>
+        <v>-2.060558</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-1.399112</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.4823</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>-0</v>
@@ -1506,49 +1506,49 @@
         <v>-0.119068</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.097908</v>
+        <v>-0.097908</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1.015279</v>
+        <v>-1.015279</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.664556</v>
+        <v>-0.664556</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.24115</v>
+        <v>-0.24115</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.199466</v>
+        <v>-0.199466</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>1.923305</v>
+        <v>-1.923305</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.307874</v>
+        <v>-0.307874</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.418264</v>
+        <v>-0.418264</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.813829</v>
+        <v>-0.813829</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.658291</v>
+        <v>-0.658291</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>1.601392</v>
+        <v>-1.601392</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>3.253992</v>
+        <v>-3.253992</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>0.404814</v>
+        <v>-0.404814</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.456605</v>
+        <v>-0.456605</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>4.897817</v>
+        <v>-4.897817</v>
       </c>
     </row>
     <row r="21">
@@ -1671,49 +1671,49 @@
         <v>-0.119068</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.097908</v>
+        <v>-0.097908</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1.015279</v>
+        <v>-1.015279</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.664556</v>
+        <v>-0.664556</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.24115</v>
+        <v>-0.24115</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.199466</v>
+        <v>-0.199466</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>1.923305</v>
+        <v>-1.923305</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.307874</v>
+        <v>-0.307874</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.418264</v>
+        <v>-0.418264</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.813829</v>
+        <v>-0.813829</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.658291</v>
+        <v>-0.658291</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>1.601392</v>
+        <v>-1.601392</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>3.253992</v>
+        <v>-3.253992</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>0.404814</v>
+        <v>-0.404814</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>0.456605</v>
+        <v>-0.456605</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>4.897817</v>
+        <v>-4.897817</v>
       </c>
     </row>
     <row r="24">
@@ -1836,16 +1836,16 @@
         <v>1.984467</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>4.8954</v>
+        <v>-4.8954</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>16.921317</v>
+        <v>-16.921317</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>7.383956</v>
+        <v>-7.383956</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>12.0575</v>
+        <v>-12.0575</v>
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>21.370056</v>
+        <v>-21.370056</v>
       </c>
       <c r="I26" s="1" t="inlineStr">
         <is>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="N26" s="3" t="n">
-        <v>108.4664</v>
+        <v>-108.4664</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>13.4938</v>
+        <v>-13.4938</v>
       </c>
       <c r="P26" s="1" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         </is>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>163.260567</v>
+        <v>-163.260567</v>
       </c>
     </row>
     <row r="27">
@@ -1917,37 +1917,37 @@
         <v>0.24115</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.199466</v>
+        <v>-0.199466</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>1.923305</v>
+        <v>-1.923305</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.307874</v>
+        <v>-0.307874</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.418264</v>
+        <v>-0.418264</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.813829</v>
+        <v>-0.813829</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.658291</v>
+        <v>-0.658291</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>1.601392</v>
+        <v>-1.601392</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>3.253992</v>
+        <v>-3.253992</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>0.404814</v>
+        <v>-0.404814</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>0.456605</v>
+        <v>-0.456605</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>4.897817</v>
+        <v>-4.897817</v>
       </c>
     </row>
     <row r="28">
@@ -2027,37 +2027,37 @@
         <v>0.24115</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.199466</v>
+        <v>-0.199466</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>1.923305</v>
+        <v>-1.923305</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.308874</v>
+        <v>-0.306874</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.418264</v>
+        <v>-0.418264</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.813829</v>
+        <v>-0.813829</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.658291</v>
+        <v>-0.658291</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>1.601392</v>
+        <v>-1.601392</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>3.253992</v>
+        <v>-3.253992</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>0.404814</v>
+        <v>-0.404814</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.456605</v>
+        <v>-0.456605</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>4.897817</v>
+        <v>-4.897817</v>
       </c>
     </row>
     <row r="30">
@@ -2157,49 +2157,49 @@
         <v>-26.57651911383255</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>2.870047135740793</v>
+        <v>197.1299528642592</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>9.529566159693747</v>
+        <v>190.4704338403063</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -5623,46 +5623,46 @@
         <v>0.092845</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.210784</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.321734</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.321734</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.321734</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.321734</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.321734</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.321734</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.321734</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.329234</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>1.527064</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>1.538764</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>1.543633</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>1.593633</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>1.781633</v>
       </c>
     </row>
     <row r="93">
@@ -9174,7 +9174,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -9890,7 +9894,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -11236,7 +11244,11 @@
           <t>Reserves 11</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
@@ -11906,7 +11918,11 @@
           <t>Reserves 13</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
@@ -12570,7 +12586,11 @@
           <t>Reserves 11</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
@@ -13344,7 +13364,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E59" s="5" t="n">
         <v>0.04083</v>
       </c>
@@ -24937,37 +24961,37 @@
         <v>0.24115</v>
       </c>
       <c r="J182" s="5" t="n">
-        <v>0.199466</v>
+        <v>-0.199466</v>
       </c>
       <c r="K182" s="5" t="n">
-        <v>1.923305</v>
+        <v>-1.923305</v>
       </c>
       <c r="L182" s="5" t="n">
-        <v>0.307874</v>
+        <v>-0.307874</v>
       </c>
       <c r="M182" s="5" t="n">
-        <v>0.418264</v>
+        <v>-0.418264</v>
       </c>
       <c r="N182" s="5" t="n">
-        <v>0.813829</v>
+        <v>-0.813829</v>
       </c>
       <c r="O182" s="5" t="n">
-        <v>0.658291</v>
+        <v>-0.658291</v>
       </c>
       <c r="P182" s="5" t="n">
-        <v>1.601392</v>
+        <v>-1.601392</v>
       </c>
       <c r="Q182" s="5" t="n">
-        <v>3.253992</v>
+        <v>-3.253992</v>
       </c>
       <c r="R182" s="5" t="n">
-        <v>0.404814</v>
+        <v>-0.404814</v>
       </c>
       <c r="S182" s="5" t="n">
-        <v>0.456605</v>
+        <v>-0.456605</v>
       </c>
       <c r="T182" s="5" t="n">
-        <v>4.897817</v>
+        <v>-4.897817</v>
       </c>
     </row>
     <row r="183">
@@ -39051,10 +39075,10 @@
         </is>
       </c>
       <c r="H331" s="5" t="n">
-        <v>0.664556</v>
+        <v>-0.664556</v>
       </c>
       <c r="I331" s="5" t="n">
-        <v>0.24115</v>
+        <v>-0.24115</v>
       </c>
       <c r="J331" t="inlineStr">
         <is>
@@ -39997,13 +40021,13 @@
         </is>
       </c>
       <c r="F341" s="5" t="n">
-        <v>0.097908</v>
+        <v>-0.097908</v>
       </c>
       <c r="G341" s="5" t="n">
-        <v>1.015279</v>
+        <v>-1.015279</v>
       </c>
       <c r="H341" s="5" t="n">
-        <v>0.664556</v>
+        <v>-0.664556</v>
       </c>
       <c r="I341" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/TAJ.xlsx
+++ b/output/pdf_financials_xlsx/TAJ.xlsx
@@ -14518,7 +14518,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E71" s="5" t="n">

--- a/output/pdf_financials_xlsx/TAJ.xlsx
+++ b/output/pdf_financials_xlsx/TAJ.xlsx
@@ -1280,10 +1280,10 @@
         <v>-0.195816</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-2.060558</v>
+        <v>0.03</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-1.399112</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>-0.4823</v>
@@ -2160,10 +2160,10 @@
         <v>200</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>197.1299528642592</v>
+        <v>2.870047135740793</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>190.4704338403063</v>
+        <v>9.529566159693747</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>200</v>
@@ -22500,7 +22500,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
           <t>-</t>
@@ -39916,7 +39920,11 @@
           <t>Income tax recovery 10</t>
         </is>
       </c>
-      <c r="D340" t="inlineStr"/>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E340" t="inlineStr">
         <is>
           <t>-</t>
